--- a/example/demo_generator/references/Household_Travel_Generate_Survey.xlsx
+++ b/example/demo_generator/references/Household_Travel_Generate_Survey.xlsx
@@ -1193,37 +1193,37 @@
     <t xml:space="preserve">No, remote studies from home or from elsewhere</t>
   </si>
   <si>
-    <t xml:space="preserve">inputRangeName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labelFrMin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labelFrMiddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labelFrMax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labelEnMin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labelEnMiddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labelEnMax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">minValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maxValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unitFr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unitEn</t>
+    <t xml:space="preserve">input_range_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_min::fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_middle::fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_max::fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_min::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_middle::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label_max::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit::fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit::en</t>
   </si>
   <si>
     <t xml:space="preserve">input_color</t>
